--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T11:58:08+00:00</t>
+    <t>2026-06-01T14:28:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3547,7 +3547,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>147</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>74</v>

--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:28:18+00:00</t>
+    <t>2026-06-01T15:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
